--- a/data/trans_orig/Q33-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q33-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según las horas al día que duerme habitualmente</t>
+          <t>Población según las horas al día que duerme habitualmente (tasa de respuesta: 98,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,57 +716,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,47</t>
+          <t>7,29; 7,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,19; 7,45</t>
+          <t>7,21; 7,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,42</t>
+          <t>7,22; 7,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,15</t>
+          <t>6,98; 7,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,3; 7,53</t>
+          <t>7,31; 7,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,1; 7,34</t>
+          <t>7,1; 7,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,44</t>
+          <t>7,2; 7,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,13</t>
+          <t>6,96; 7,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,33; 7,46</t>
+          <t>7,32; 7,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,2; 7,36</t>
+          <t>7,19; 7,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,24; 7,4</t>
+          <t>7,25; 7,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -856,47 +856,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 7,64</t>
+          <t>7,46; 7,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 7,44</t>
+          <t>7,16; 7,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,2; 7,44</t>
+          <t>7,21; 7,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,06; 7,25</t>
+          <t>7,05; 7,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,35; 7,56</t>
+          <t>7,35; 7,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 7,27</t>
+          <t>7,02; 7,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,44</t>
+          <t>7,22; 7,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 7,1</t>
+          <t>6,9; 7,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 7,56</t>
+          <t>7,43; 7,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,42</t>
+          <t>7,24; 7,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,42; 7,59</t>
+          <t>7,42; 7,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,17; 7,38</t>
+          <t>7,18; 7,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,93; 8,54</t>
+          <t>6,93; 8,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,06; 7,46</t>
+          <t>7,04; 7,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1026,17 +1026,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,39</t>
+          <t>6,98; 7,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,84; 7,11</t>
+          <t>6,85; 7,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,37; 7,52</t>
+          <t>7,36; 7,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,94; 8,36</t>
+          <t>6,95; 8,37</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,37; 7,5</t>
+          <t>7,37; 7,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,41</t>
+          <t>7,27; 7,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 7,5</t>
+          <t>7,35; 7,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,06; 7,22</t>
+          <t>7,06; 7,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,34; 7,51</t>
+          <t>7,34; 7,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,1; 7,3</t>
+          <t>7,12; 7,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 7,33</t>
+          <t>7,15; 7,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 6,97</t>
+          <t>6,38; 6,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,38; 7,49</t>
+          <t>7,39; 7,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,22; 7,35</t>
+          <t>7,23; 7,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,4</t>
+          <t>7,3; 7,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,65; 7,08</t>
+          <t>6,64; 7,08</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,53; 7,78</t>
+          <t>7,52; 7,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1286,22 +1286,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 7,62</t>
+          <t>7,42; 7,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,04; 7,27</t>
+          <t>7,03; 7,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,49</t>
+          <t>7,28; 7,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,16</t>
+          <t>6,96; 7,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,41; 7,57</t>
+          <t>7,4; 7,56</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,15; 7,31</t>
+          <t>7,14; 7,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,04; 8,24</t>
+          <t>8,03; 8,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,9; 8,2</t>
+          <t>7,91; 8,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,56; 7,99</t>
+          <t>7,55; 8,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,3; 7,45</t>
+          <t>7,29; 7,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,22; 7,39</t>
+          <t>7,22; 7,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,16; 7,33</t>
+          <t>7,17; 7,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,34; 7,49</t>
+          <t>7,35; 7,49</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,39; 7,54</t>
+          <t>7,39; 7,53</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,3; 7,47</t>
+          <t>7,3; 7,46</t>
         </is>
       </c>
     </row>
@@ -1561,27 +1561,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,35; 7,43</t>
+          <t>7,35; 7,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,43; 7,51</t>
+          <t>7,42; 7,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,14; 7,74</t>
+          <t>7,15; 7,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,35; 7,43</t>
+          <t>7,35; 7,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,14; 7,23</t>
+          <t>7,13; 7,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,75; 7,04</t>
+          <t>6,77; 7,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,32</t>
+          <t>7,25; 7,32</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,03; 7,35</t>
+          <t>7,04; 7,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q33-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q33-Clase-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,07</t>
+          <t>7,09</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,06</t>
+          <t>7,08</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,44</t>
+          <t>7,2; 7,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,22; 7,44</t>
+          <t>7,2; 7,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,14</t>
+          <t>7,01; 7,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,1; 7,36</t>
+          <t>7,09; 7,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,27 +751,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 7,13</t>
+          <t>6,97; 7,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 7,47</t>
+          <t>7,32; 7,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,19; 7,37</t>
+          <t>7,19; 7,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,25; 7,4</t>
+          <t>7,25; 7,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,0; 7,12</t>
+          <t>7,01; 7,13</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,15</t>
+          <t>7,17</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,0</t>
+          <t>7,01</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,08</t>
+          <t>7,1</t>
         </is>
       </c>
     </row>
@@ -856,22 +856,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 7,65</t>
+          <t>7,45; 7,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 7,42</t>
+          <t>7,15; 7,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,45</t>
+          <t>7,2; 7,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,05; 7,25</t>
+          <t>7,07; 7,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,02; 7,26</t>
+          <t>7,0; 7,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -891,27 +891,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,9; 7,1</t>
+          <t>6,92; 7,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 7,56</t>
+          <t>7,42; 7,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,12; 7,31</t>
+          <t>7,12; 7,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,24; 7,41</t>
+          <t>7,25; 7,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,02; 7,15</t>
+          <t>7,03; 7,16</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,72</t>
+          <t>7,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,98</t>
+          <t>6,99</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,57</t>
+          <t>7,0</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,42; 7,6</t>
+          <t>7,42; 7,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1011,22 +1011,22 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,93; 8,49</t>
+          <t>6,89; 7,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,04; 7,47</t>
+          <t>7,06; 7,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,93; 7,25</t>
+          <t>6,93; 7,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,42</t>
+          <t>6,97; 7,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,36; 7,53</t>
+          <t>7,37; 7,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,23; 7,42</t>
+          <t>7,22; 7,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,95; 8,37</t>
+          <t>6,91; 7,08</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,14</t>
+          <t>7,16</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,75</t>
+          <t>6,96</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,95</t>
+          <t>7,07</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,37; 7,51</t>
+          <t>7,36; 7,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 7,41</t>
+          <t>7,26; 7,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,06; 7,23</t>
+          <t>7,08; 7,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,22 +1161,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,12; 7,31</t>
+          <t>7,12; 7,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 7,32</t>
+          <t>7,14; 7,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,38; 6,98</t>
+          <t>6,87; 7,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,39; 7,5</t>
+          <t>7,38; 7,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,3; 7,4</t>
+          <t>7,29; 7,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,64; 7,08</t>
+          <t>7,02; 7,12</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,14</t>
+          <t>7,12</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1281,17 +1281,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,35; 7,59</t>
+          <t>7,36; 7,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 7,62</t>
+          <t>7,42; 7,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,03; 7,26</t>
+          <t>7,02; 7,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1306,12 +1306,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,03; 7,22</t>
+          <t>7,03; 7,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,86; 7,0</t>
+          <t>6,86; 7,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,14; 7,32</t>
+          <t>7,15; 7,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,81</t>
+          <t>7,78</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,38</t>
+          <t>7,37</t>
         </is>
       </c>
     </row>
@@ -1426,22 +1426,22 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,95; 8,19</t>
+          <t>7,96; 8,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,55; 8,0</t>
+          <t>7,55; 7,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,44</t>
+          <t>7,3; 7,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,18; 7,35</t>
+          <t>7,17; 7,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,17; 7,33</t>
+          <t>7,18; 7,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,45; 7,59</t>
+          <t>7,46; 7,58</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,35; 7,49</t>
+          <t>7,34; 7,49</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,3; 7,46</t>
+          <t>7,29; 7,45</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,3</t>
+          <t>7,17</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,97</t>
+          <t>7,04</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,13</t>
+          <t>7,1</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,5; 7,58</t>
+          <t>7,51; 7,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1566,17 +1566,17 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,42; 7,51</t>
+          <t>7,43; 7,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,15; 7,87</t>
+          <t>7,12; 7,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,35; 7,44</t>
+          <t>7,35; 7,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,77; 7,05</t>
+          <t>7,0; 7,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,44; 7,5</t>
+          <t>7,44; 7,49</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,04; 7,37</t>
+          <t>7,08; 7,13</t>
         </is>
       </c>
     </row>
